--- a/data/trans_orig/P32E$bar_2023-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P32E$bar_2023-Clase-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según los lugares donde se realiza el consumo de alcohol (atracón) (multirrespuesta) en 2023</t>
+          <t>Población según los lugares donde se realiza el consumo de alcohol (atracón) (multirrespuesta) en 2023 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>8683</t>
+          <t>9025</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>16776</t>
+          <t>16542</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>45,22%</t>
+          <t>47,0%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>87,37%</t>
+          <t>86,15%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,7 +765,7 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>2978</t>
+          <t>2976</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
@@ -780,7 +780,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>47,82%</t>
+          <t>47,79%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>14040</t>
+          <t>13854</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>22292</t>
+          <t>22488</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>55,21%</t>
+          <t>54,48%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>87,67%</t>
+          <t>88,44%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>7675</t>
+          <t>7892</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>16133</t>
+          <t>16283</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>39,97%</t>
+          <t>41,1%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>84,02%</t>
+          <t>84,8%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>393</t>
+          <t>390</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>5857</t>
+          <t>5852</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>6,31%</t>
+          <t>6,26%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>94,04%</t>
+          <t>93,97%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>9913</t>
+          <t>9872</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>19399</t>
+          <t>19797</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>38,98%</t>
+          <t>38,82%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>76,29%</t>
+          <t>77,86%</t>
         </is>
       </c>
     </row>
@@ -956,12 +956,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>2014</t>
+          <t>1895</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>11117</t>
+          <t>10765</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -971,12 +971,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>10,49%</t>
+          <t>9,87%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>57,9%</t>
+          <t>56,07%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -996,7 +996,7 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>5099</t>
+          <t>5100</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>81,88%</t>
+          <t>81,9%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1026,12 +1026,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>2878</t>
+          <t>2600</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>13644</t>
+          <t>13430</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1041,12 +1041,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>11,32%</t>
+          <t>10,23%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>53,66%</t>
+          <t>52,82%</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>6425</t>
+          <t>5963</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1089,7 +1089,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>33,46%</t>
+          <t>31,05%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1109,7 +1109,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>5099</t>
+          <t>5100</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>81,88%</t>
+          <t>81,9%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1144,7 +1144,7 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>9214</t>
+          <t>8947</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1159,7 +1159,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>36,24%</t>
+          <t>35,19%</t>
         </is>
       </c>
     </row>
@@ -1187,7 +1187,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>6462</t>
+          <t>6846</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>33,66%</t>
+          <t>35,66%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1222,7 +1222,7 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>5099</t>
+          <t>5100</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1237,7 +1237,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>81,88%</t>
+          <t>81,9%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1252,12 +1252,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1032</t>
+          <t>1017</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>9654</t>
+          <t>9908</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1267,12 +1267,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>4,06%</t>
+          <t>4,0%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>37,97%</t>
+          <t>38,97%</t>
         </is>
       </c>
     </row>
@@ -1299,12 +1299,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>3758</t>
+          <t>3417</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>10635</t>
+          <t>10366</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1314,12 +1314,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>27,55%</t>
+          <t>25,05%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>77,96%</t>
+          <t>75,99%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1334,12 +1334,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>6034</t>
+          <t>6336</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>10722</t>
+          <t>11006</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1349,12 +1349,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>51,91%</t>
+          <t>54,5%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>92,23%</t>
+          <t>94,68%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1369,12 +1369,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>10973</t>
+          <t>11297</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>19922</t>
+          <t>20283</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1384,12 +1384,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>43,43%</t>
+          <t>44,71%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>78,85%</t>
+          <t>80,27%</t>
         </is>
       </c>
     </row>
@@ -1412,12 +1412,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>3153</t>
+          <t>3231</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>9935</t>
+          <t>10069</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1427,12 +1427,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>23,11%</t>
+          <t>23,68%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>72,83%</t>
+          <t>73,82%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1447,12 +1447,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>2852</t>
+          <t>2846</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>9307</t>
+          <t>9331</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1462,12 +1462,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>24,54%</t>
+          <t>24,48%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>80,06%</t>
+          <t>80,26%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1482,12 +1482,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>8006</t>
+          <t>7785</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>17877</t>
+          <t>17573</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1497,12 +1497,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>31,69%</t>
+          <t>30,81%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>70,75%</t>
+          <t>69,55%</t>
         </is>
       </c>
     </row>
@@ -1525,12 +1525,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1037</t>
+          <t>996</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>7272</t>
+          <t>7325</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1540,12 +1540,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>7,6%</t>
+          <t>7,3%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>53,31%</t>
+          <t>53,7%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1560,12 +1560,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>1312</t>
+          <t>877</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>7976</t>
+          <t>8062</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1575,12 +1575,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>11,28%</t>
+          <t>7,55%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>68,61%</t>
+          <t>69,35%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1595,12 +1595,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>3641</t>
+          <t>3791</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>13320</t>
+          <t>13283</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1610,12 +1610,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>14,41%</t>
+          <t>15,0%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>52,72%</t>
+          <t>52,57%</t>
         </is>
       </c>
     </row>
@@ -1643,7 +1643,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>6503</t>
+          <t>6015</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1658,7 +1658,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>47,67%</t>
+          <t>44,09%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1678,7 +1678,7 @@
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>5587</t>
+          <t>5776</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1693,7 +1693,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>48,06%</t>
+          <t>49,69%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1708,12 +1708,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1018</t>
+          <t>949</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>8165</t>
+          <t>8644</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1723,12 +1723,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>4,03%</t>
+          <t>3,75%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>32,31%</t>
+          <t>34,21%</t>
         </is>
       </c>
     </row>
@@ -1756,7 +1756,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>3580</t>
+          <t>4274</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1771,7 +1771,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>26,24%</t>
+          <t>31,33%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1791,7 +1791,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>6000</t>
+          <t>6144</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1806,7 +1806,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>51,61%</t>
+          <t>52,85%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1821,12 +1821,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>840</t>
+          <t>849</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>8058</t>
+          <t>7955</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1836,12 +1836,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,33%</t>
+          <t>3,36%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>31,89%</t>
+          <t>31,48%</t>
         </is>
       </c>
     </row>
@@ -1868,12 +1868,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>17624</t>
+          <t>18182</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>26719</t>
+          <t>26865</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1883,12 +1883,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>60,18%</t>
+          <t>62,08%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>91,23%</t>
+          <t>91,73%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1938,12 +1938,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>19427</t>
+          <t>18792</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>28006</t>
+          <t>28068</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1953,12 +1953,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>61,7%</t>
+          <t>59,69%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>88,95%</t>
+          <t>89,15%</t>
         </is>
       </c>
     </row>
@@ -1981,12 +1981,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>6041</t>
+          <t>5468</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>17727</t>
+          <t>16434</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1996,12 +1996,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>20,63%</t>
+          <t>18,67%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>60,53%</t>
+          <t>56,12%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2051,12 +2051,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>6922</t>
+          <t>7003</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>18263</t>
+          <t>18177</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2066,12 +2066,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>21,99%</t>
+          <t>22,24%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>58,01%</t>
+          <t>57,73%</t>
         </is>
       </c>
     </row>
@@ -2094,12 +2094,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>820</t>
+          <t>863</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>9026</t>
+          <t>8566</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2109,12 +2109,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>2,95%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>30,82%</t>
+          <t>29,25%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2129,12 +2129,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>672</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2144,12 +2144,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>30,57%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2164,12 +2164,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>893</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>8364</t>
+          <t>9045</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2179,12 +2179,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>2,84%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>26,56%</t>
+          <t>28,73%</t>
         </is>
       </c>
     </row>
@@ -2212,7 +2212,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>5551</t>
+          <t>5817</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2227,7 +2227,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>18,95%</t>
+          <t>19,86%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2242,12 +2242,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>672</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2257,12 +2257,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>30,57%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2282,7 +2282,7 @@
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>5418</t>
+          <t>5262</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2297,7 +2297,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>17,21%</t>
+          <t>16,71%</t>
         </is>
       </c>
     </row>
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>2066</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2335,12 +2335,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>7,06%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2355,12 +2355,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>672</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2370,12 +2370,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>30,57%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2390,12 +2390,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1877</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2405,12 +2405,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>5,96%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -2437,12 +2437,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>19835</t>
+          <t>20476</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>32248</t>
+          <t>32310</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2452,12 +2452,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>51,29%</t>
+          <t>52,95%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>83,4%</t>
+          <t>83,56%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2472,12 +2472,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>5495</t>
+          <t>5111</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>10075</t>
+          <t>10023</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2487,12 +2487,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>51,77%</t>
+          <t>48,15%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>94,91%</t>
+          <t>94,42%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2507,12 +2507,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>28737</t>
+          <t>27645</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>41037</t>
+          <t>41061</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2522,12 +2522,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>58,31%</t>
+          <t>56,09%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>83,27%</t>
+          <t>83,31%</t>
         </is>
       </c>
     </row>
@@ -2550,12 +2550,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>14078</t>
+          <t>14855</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>27267</t>
+          <t>26880</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2565,12 +2565,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>36,41%</t>
+          <t>38,42%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>70,51%</t>
+          <t>69,51%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2585,12 +2585,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1084</t>
+          <t>1040</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>5817</t>
+          <t>5726</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2600,12 +2600,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>10,21%</t>
+          <t>9,8%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>54,8%</t>
+          <t>53,94%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2620,12 +2620,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>17443</t>
+          <t>17687</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>30832</t>
+          <t>30244</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2635,12 +2635,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>35,39%</t>
+          <t>35,89%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>62,56%</t>
+          <t>61,37%</t>
         </is>
       </c>
     </row>
@@ -2663,12 +2663,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>2531</t>
+          <t>2564</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>14518</t>
+          <t>14112</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2678,12 +2678,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>6,54%</t>
+          <t>6,63%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>37,54%</t>
+          <t>36,49%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2698,12 +2698,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>168</t>
+          <t>163</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>3934</t>
+          <t>3748</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2713,12 +2713,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>1,54%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>37,06%</t>
+          <t>35,31%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>3953</t>
+          <t>3976</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>15430</t>
+          <t>17092</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2748,12 +2748,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>8,02%</t>
+          <t>8,07%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>31,31%</t>
+          <t>34,68%</t>
         </is>
       </c>
     </row>
@@ -2781,7 +2781,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>8501</t>
+          <t>8400</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>21,98%</t>
+          <t>21,72%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2811,12 +2811,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>1060</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>9,99%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2851,7 +2851,7 @@
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>9267</t>
+          <t>8604</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>18,8%</t>
+          <t>17,46%</t>
         </is>
       </c>
     </row>
@@ -2889,12 +2889,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>1719</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2904,12 +2904,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>4,44%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2929,7 +2929,7 @@
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>4083</t>
+          <t>4240</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2944,7 +2944,7 @@
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>38,47%</t>
+          <t>39,94%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2964,7 +2964,7 @@
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>4826</t>
+          <t>5677</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2979,7 +2979,7 @@
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>9,79%</t>
+          <t>11,52%</t>
         </is>
       </c>
     </row>
@@ -3006,12 +3006,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>11904</t>
+          <t>11796</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>24506</t>
+          <t>25142</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3021,12 +3021,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>35,99%</t>
+          <t>35,66%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>74,09%</t>
+          <t>76,01%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3041,12 +3041,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>2660</t>
+          <t>2345</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>6943</t>
+          <t>6950</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3056,12 +3056,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>32,88%</t>
+          <t>28,99%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>85,84%</t>
+          <t>85,92%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3076,12 +3076,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>16860</t>
+          <t>16657</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>30287</t>
+          <t>30104</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3091,12 +3091,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>40,96%</t>
+          <t>40,47%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>73,57%</t>
+          <t>73,13%</t>
         </is>
       </c>
     </row>
@@ -3119,12 +3119,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>15054</t>
+          <t>14980</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>28750</t>
+          <t>28683</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3134,12 +3134,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>45,51%</t>
+          <t>45,29%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>86,92%</t>
+          <t>86,72%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3154,12 +3154,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>1454</t>
+          <t>1509</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>6179</t>
+          <t>6249</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>17,98%</t>
+          <t>18,65%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>76,39%</t>
+          <t>77,26%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3189,12 +3189,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>18326</t>
+          <t>17665</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>32732</t>
+          <t>32683</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>44,52%</t>
+          <t>42,91%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>79,51%</t>
+          <t>79,39%</t>
         </is>
       </c>
     </row>
@@ -3232,12 +3232,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>5989</t>
+          <t>5892</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>18929</t>
+          <t>19577</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3247,12 +3247,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>18,11%</t>
+          <t>17,81%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>57,23%</t>
+          <t>59,19%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3267,7 +3267,7 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>1241</t>
+          <t>1120</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>15,34%</t>
+          <t>13,85%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>74,55%</t>
+          <t>74,54%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3302,12 +3302,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>9092</t>
+          <t>9183</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>23376</t>
+          <t>23557</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>22,09%</t>
+          <t>22,31%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>56,79%</t>
+          <t>57,22%</t>
         </is>
       </c>
     </row>
@@ -3345,12 +3345,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>8785</t>
+          <t>8666</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>21642</t>
+          <t>21621</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3360,12 +3360,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>26,56%</t>
+          <t>26,2%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>65,43%</t>
+          <t>65,37%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3380,12 +3380,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>639</t>
+          <t>959</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>5247</t>
+          <t>5450</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3395,12 +3395,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>7,9%</t>
+          <t>11,85%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>64,87%</t>
+          <t>67,38%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3415,12 +3415,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>11546</t>
+          <t>11674</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>25518</t>
+          <t>25062</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3430,12 +3430,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>28,05%</t>
+          <t>28,36%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>61,99%</t>
+          <t>60,88%</t>
         </is>
       </c>
     </row>
@@ -3458,12 +3458,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>1856</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3473,12 +3473,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>5,61%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3493,12 +3493,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>1173</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3508,12 +3508,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>14,51%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3528,12 +3528,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>1711</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3543,12 +3543,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>4,16%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -3610,7 +3610,7 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>5588</t>
+          <t>5565</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
@@ -3625,7 +3625,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>46,29%</t>
+          <t>46,1%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3645,12 +3645,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>8869</t>
+          <t>8251</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>17639</t>
+          <t>17585</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3660,12 +3660,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>47,41%</t>
+          <t>44,1%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>94,28%</t>
+          <t>93,99%</t>
         </is>
       </c>
     </row>
@@ -3693,7 +3693,7 @@
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>2960</t>
+          <t>6637</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3708,7 +3708,7 @@
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>44,6%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3728,7 +3728,7 @@
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>6676</t>
+          <t>6945</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3743,7 +3743,7 @@
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>55,3%</t>
+          <t>57,53%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3758,12 +3758,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>496</t>
+          <t>517</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>8681</t>
+          <t>8295</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3773,12 +3773,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>2,76%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>46,4%</t>
+          <t>44,34%</t>
         </is>
       </c>
     </row>
@@ -3841,7 +3841,7 @@
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>4906</t>
+          <t>5004</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3856,7 +3856,7 @@
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>40,64%</t>
+          <t>41,45%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3876,7 +3876,7 @@
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>9885</t>
+          <t>8886</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3891,7 +3891,7 @@
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>52,83%</t>
+          <t>47,49%</t>
         </is>
       </c>
     </row>
@@ -3954,7 +3954,7 @@
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>4736</t>
+          <t>5823</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3969,7 +3969,7 @@
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>39,23%</t>
+          <t>48,23%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3984,12 +3984,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>1033</t>
+          <t>927</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>11525</t>
+          <t>10483</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3999,12 +3999,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>5,52%</t>
+          <t>4,96%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>61,6%</t>
+          <t>56,03%</t>
         </is>
       </c>
     </row>
@@ -4027,12 +4027,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>2406</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -4042,12 +4042,12 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>36,25%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -4062,12 +4062,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>2262</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -4077,12 +4077,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>18,74%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -4097,12 +4097,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>2524</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -4112,12 +4112,12 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>13,49%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -4144,12 +4144,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>80679</t>
+          <t>80012</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>104633</t>
+          <t>104592</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4159,12 +4159,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>57,42%</t>
+          <t>56,94%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>74,47%</t>
+          <t>74,44%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4179,12 +4179,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>33292</t>
+          <t>33872</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>43872</t>
+          <t>43767</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4194,12 +4194,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>65,5%</t>
+          <t>66,64%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>86,32%</t>
+          <t>86,11%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4214,12 +4214,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>118311</t>
+          <t>119980</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>145646</t>
+          <t>146072</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4229,12 +4229,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>61,83%</t>
+          <t>62,71%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>76,12%</t>
+          <t>76,34%</t>
         </is>
       </c>
     </row>
@@ -4257,12 +4257,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>59811</t>
+          <t>61086</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>86615</t>
+          <t>86451</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4272,12 +4272,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>42,57%</t>
+          <t>43,47%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>61,64%</t>
+          <t>61,53%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4292,12 +4292,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>12952</t>
+          <t>12837</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>25710</t>
+          <t>26644</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -4307,12 +4307,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>25,48%</t>
+          <t>25,26%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>50,58%</t>
+          <t>52,42%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4327,12 +4327,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>77498</t>
+          <t>78732</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>106938</t>
+          <t>107637</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -4342,12 +4342,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>40,5%</t>
+          <t>41,15%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>55,89%</t>
+          <t>56,26%</t>
         </is>
       </c>
     </row>
@@ -4370,12 +4370,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>23158</t>
+          <t>23269</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>46386</t>
+          <t>46678</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4385,12 +4385,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>16,48%</t>
+          <t>16,56%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>33,01%</t>
+          <t>33,22%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4405,12 +4405,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>6482</t>
+          <t>6321</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>19007</t>
+          <t>19064</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4420,12 +4420,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>12,75%</t>
+          <t>12,44%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>37,4%</t>
+          <t>37,51%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4440,12 +4440,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>33212</t>
+          <t>32573</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>60639</t>
+          <t>59928</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4455,12 +4455,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>17,36%</t>
+          <t>17,02%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>31,69%</t>
+          <t>31,32%</t>
         </is>
       </c>
     </row>
@@ -4483,12 +4483,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>16888</t>
+          <t>16138</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>38969</t>
+          <t>37647</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4498,12 +4498,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>12,02%</t>
+          <t>11,49%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>27,73%</t>
+          <t>26,79%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4518,12 +4518,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>3306</t>
+          <t>3392</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>13675</t>
+          <t>13819</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4533,12 +4533,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>6,5%</t>
+          <t>6,67%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>26,9%</t>
+          <t>27,19%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4553,12 +4553,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>22680</t>
+          <t>22828</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>46532</t>
+          <t>46419</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4568,12 +4568,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>11,85%</t>
+          <t>11,93%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>24,32%</t>
+          <t>24,26%</t>
         </is>
       </c>
     </row>
@@ -4596,12 +4596,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>877</t>
+          <t>848</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>8555</t>
+          <t>7287</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -4611,12 +4611,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>6,09%</t>
+          <t>5,19%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -4631,12 +4631,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>1213</t>
+          <t>1236</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>11968</t>
+          <t>11411</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -4646,12 +4646,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>2,43%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>23,55%</t>
+          <t>22,45%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -4666,12 +4666,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>3163</t>
+          <t>3440</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>15550</t>
+          <t>15686</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -4681,12 +4681,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>8,13%</t>
+          <t>8,2%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P32E$bar_2023-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P32E$bar_2023-Clase-trans_orig.xlsx
@@ -725,32 +725,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>13499</t>
+          <t>14314</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>9025</t>
+          <t>9657</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>16542</t>
+          <t>17889</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>70,3%</t>
+          <t>70,05%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>47,0%</t>
+          <t>47,26%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>86,15%</t>
+          <t>87,54%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -760,27 +760,27 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>5569</t>
+          <t>5220</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>2976</t>
+          <t>2780</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>6228</t>
+          <t>6478</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>89,42%</t>
+          <t>80,58%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>47,79%</t>
+          <t>42,92%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>19068</t>
+          <t>19534</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>13854</t>
+          <t>14117</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>22488</t>
+          <t>23426</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>74,99%</t>
+          <t>72,58%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>54,48%</t>
+          <t>52,46%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>88,44%</t>
+          <t>87,05%</t>
         </is>
       </c>
     </row>
@@ -838,32 +838,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>12323</t>
+          <t>13309</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>7892</t>
+          <t>8488</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>16283</t>
+          <t>17458</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>64,18%</t>
+          <t>65,13%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>41,1%</t>
+          <t>41,54%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>84,8%</t>
+          <t>85,43%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>2393</t>
+          <t>2965</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>390</t>
+          <t>652</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>5852</t>
+          <t>5506</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>38,43%</t>
+          <t>45,78%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>6,26%</t>
+          <t>10,07%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>93,97%</t>
+          <t>84,99%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>14715</t>
+          <t>16274</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>9872</t>
+          <t>10754</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>19797</t>
+          <t>21329</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>57,87%</t>
+          <t>60,47%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>38,82%</t>
+          <t>39,96%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>77,86%</t>
+          <t>79,26%</t>
         </is>
       </c>
     </row>
@@ -951,32 +951,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>5566</t>
+          <t>6111</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1895</t>
+          <t>2322</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>10765</t>
+          <t>11774</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>28,99%</t>
+          <t>29,9%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>9,87%</t>
+          <t>11,36%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>56,07%</t>
+          <t>57,62%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>1734</t>
+          <t>1707</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
@@ -996,12 +996,12 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>5100</t>
+          <t>5116</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>27,85%</t>
+          <t>26,36%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>81,9%</t>
+          <t>78,97%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>7300</t>
+          <t>7818</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>2600</t>
+          <t>3425</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>13430</t>
+          <t>14962</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>28,71%</t>
+          <t>29,05%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>10,23%</t>
+          <t>12,73%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>52,82%</t>
+          <t>55,6%</t>
         </is>
       </c>
     </row>
@@ -1064,7 +1064,7 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1219</t>
+          <t>1310</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -1074,12 +1074,12 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>5963</t>
+          <t>5678</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>6,35%</t>
+          <t>6,41%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -1089,7 +1089,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>31,05%</t>
+          <t>27,78%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1099,7 +1099,7 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>1734</t>
+          <t>1707</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>5100</t>
+          <t>5116</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>27,85%</t>
+          <t>26,36%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>81,9%</t>
+          <t>78,97%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1134,7 +1134,7 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>2953</t>
+          <t>3018</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
@@ -1144,12 +1144,12 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>8947</t>
+          <t>9024</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>11,61%</t>
+          <t>11,21%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
@@ -1159,7 +1159,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>35,19%</t>
+          <t>33,53%</t>
         </is>
       </c>
     </row>
@@ -1177,7 +1177,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>2097</t>
+          <t>2037</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -1187,12 +1187,12 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>6846</t>
+          <t>6818</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>10,92%</t>
+          <t>9,97%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>35,66%</t>
+          <t>33,36%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1212,7 +1212,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>1734</t>
+          <t>1707</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
@@ -1222,12 +1222,12 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>5100</t>
+          <t>5116</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>27,85%</t>
+          <t>26,36%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
@@ -1237,7 +1237,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>81,9%</t>
+          <t>78,97%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1247,32 +1247,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>3832</t>
+          <t>3744</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1017</t>
+          <t>958</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>9908</t>
+          <t>8981</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>15,07%</t>
+          <t>13,91%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>3,56%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>38,97%</t>
+          <t>33,37%</t>
         </is>
       </c>
     </row>
@@ -1294,32 +1294,32 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>7138</t>
+          <t>7557</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>3417</t>
+          <t>3871</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>10366</t>
+          <t>11517</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>52,33%</t>
+          <t>49,3%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>25,05%</t>
+          <t>25,25%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>75,99%</t>
+          <t>75,13%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1329,32 +1329,32 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>9066</t>
+          <t>9839</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>6336</t>
+          <t>6358</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>11006</t>
+          <t>12105</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>77,99%</t>
+          <t>73,55%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>54,5%</t>
+          <t>47,53%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>94,68%</t>
+          <t>90,49%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1364,32 +1364,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>16205</t>
+          <t>17396</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>11297</t>
+          <t>11983</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>20283</t>
+          <t>22168</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>64,13%</t>
+          <t>60,6%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>44,71%</t>
+          <t>41,74%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>80,27%</t>
+          <t>77,23%</t>
         </is>
       </c>
     </row>
@@ -1407,32 +1407,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>6685</t>
+          <t>7934</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>3231</t>
+          <t>3931</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>10069</t>
+          <t>11486</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>49,0%</t>
+          <t>51,76%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>23,68%</t>
+          <t>25,64%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>73,82%</t>
+          <t>74,93%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1442,32 +1442,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>6191</t>
+          <t>7087</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>2846</t>
+          <t>3421</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>9331</t>
+          <t>10717</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>53,25%</t>
+          <t>52,98%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>24,48%</t>
+          <t>25,57%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>80,26%</t>
+          <t>80,11%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1477,32 +1477,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>12876</t>
+          <t>15022</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>7785</t>
+          <t>9726</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>17573</t>
+          <t>20570</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>50,96%</t>
+          <t>52,33%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>30,81%</t>
+          <t>33,88%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>69,55%</t>
+          <t>71,66%</t>
         </is>
       </c>
     </row>
@@ -1520,32 +1520,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>3787</t>
+          <t>4186</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>996</t>
+          <t>1071</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>7325</t>
+          <t>8187</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>27,76%</t>
+          <t>27,3%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>7,3%</t>
+          <t>6,99%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>53,7%</t>
+          <t>53,41%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1555,32 +1555,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>4162</t>
+          <t>4969</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>877</t>
+          <t>1396</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>8062</t>
+          <t>8673</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>35,8%</t>
+          <t>37,14%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>7,55%</t>
+          <t>10,43%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>69,35%</t>
+          <t>64,83%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1590,32 +1590,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>7949</t>
+          <t>9154</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>3791</t>
+          <t>4498</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>13283</t>
+          <t>14936</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>31,46%</t>
+          <t>31,89%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>15,0%</t>
+          <t>15,67%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>52,57%</t>
+          <t>52,03%</t>
         </is>
       </c>
     </row>
@@ -1633,7 +1633,7 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>1880</t>
+          <t>2172</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -1643,12 +1643,12 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>6015</t>
+          <t>6757</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>13,78%</t>
+          <t>14,17%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
@@ -1658,7 +1658,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>44,09%</t>
+          <t>44,08%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1668,7 +1668,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>1779</t>
+          <t>1963</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
@@ -1678,12 +1678,12 @@
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>5776</t>
+          <t>6696</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>15,31%</t>
+          <t>14,67%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
@@ -1693,7 +1693,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>49,69%</t>
+          <t>50,05%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1703,32 +1703,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>3659</t>
+          <t>4135</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>949</t>
+          <t>1323</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>8644</t>
+          <t>9660</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>14,48%</t>
+          <t>14,4%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>3,75%</t>
+          <t>4,61%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>34,21%</t>
+          <t>33,65%</t>
         </is>
       </c>
     </row>
@@ -1746,7 +1746,7 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>874</t>
+          <t>1056</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1756,12 +1756,12 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>4274</t>
+          <t>5372</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>6,4%</t>
+          <t>6,89%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -1771,7 +1771,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>31,33%</t>
+          <t>35,04%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>2274</t>
+          <t>2413</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
@@ -1791,12 +1791,12 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>6144</t>
+          <t>6462</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>19,56%</t>
+          <t>18,04%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
@@ -1806,7 +1806,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>52,85%</t>
+          <t>48,31%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1816,32 +1816,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>3147</t>
+          <t>3469</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>849</t>
+          <t>1036</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>7955</t>
+          <t>8675</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>12,46%</t>
+          <t>12,08%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,36%</t>
+          <t>3,61%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>31,48%</t>
+          <t>30,22%</t>
         </is>
       </c>
     </row>
@@ -1863,32 +1863,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>23132</t>
+          <t>25490</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>18182</t>
+          <t>19442</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>26865</t>
+          <t>29087</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>78,99%</t>
+          <t>79,74%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>62,08%</t>
+          <t>60,82%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>91,73%</t>
+          <t>90,99%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1898,27 +1898,27 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>1315</t>
+          <t>2005</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>540</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>2198</t>
+          <t>3547</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>59,8%</t>
+          <t>56,53%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>15,22%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -1933,32 +1933,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>24447</t>
+          <t>27495</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>18792</t>
+          <t>21682</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>28068</t>
+          <t>31693</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>77,65%</t>
+          <t>77,42%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>59,69%</t>
+          <t>61,05%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>89,15%</t>
+          <t>89,24%</t>
         </is>
       </c>
     </row>
@@ -1976,32 +1976,32 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>10922</t>
+          <t>11397</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>5468</t>
+          <t>6199</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>16434</t>
+          <t>18245</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>37,3%</t>
+          <t>35,65%</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>18,67%</t>
+          <t>19,39%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>56,12%</t>
+          <t>57,08%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2011,7 +2011,7 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>883</t>
+          <t>1542</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
@@ -2021,12 +2021,12 @@
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>2198</t>
+          <t>3007</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>40,2%</t>
+          <t>43,47%</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
@@ -2036,7 +2036,7 @@
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>84,78%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2046,32 +2046,32 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>11806</t>
+          <t>12939</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>7003</t>
+          <t>7367</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>18177</t>
+          <t>19353</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
         <is>
-          <t>37,5%</t>
+          <t>36,43%</t>
         </is>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>22,24%</t>
+          <t>20,74%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>57,73%</t>
+          <t>54,49%</t>
         </is>
       </c>
     </row>
@@ -2089,32 +2089,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>3191</t>
+          <t>3347</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>863</t>
+          <t>769</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>8566</t>
+          <t>8685</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>10,9%</t>
+          <t>10,47%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,95%</t>
+          <t>2,41%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>29,25%</t>
+          <t>27,17%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2159,32 +2159,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>3191</t>
+          <t>3347</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>893</t>
+          <t>923</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>9045</t>
+          <t>8743</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>10,14%</t>
+          <t>9,42%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,84%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>28,73%</t>
+          <t>24,62%</t>
         </is>
       </c>
     </row>
@@ -2202,7 +2202,7 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>1201</t>
+          <t>1229</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
@@ -2212,12 +2212,12 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>5817</t>
+          <t>5297</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>4,1%</t>
+          <t>3,85%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
@@ -2227,7 +2227,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>19,86%</t>
+          <t>16,57%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2272,7 +2272,7 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>1201</t>
+          <t>1229</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
@@ -2282,12 +2282,12 @@
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>5262</t>
+          <t>5415</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>3,82%</t>
+          <t>3,46%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
@@ -2297,7 +2297,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>16,71%</t>
+          <t>15,25%</t>
         </is>
       </c>
     </row>
@@ -2432,32 +2432,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>27173</t>
+          <t>28955</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>20476</t>
+          <t>22176</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>32310</t>
+          <t>34512</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>70,27%</t>
+          <t>69,25%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>52,95%</t>
+          <t>53,04%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>83,56%</t>
+          <t>82,54%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2467,32 +2467,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>8448</t>
+          <t>11844</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>5111</t>
+          <t>8152</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>10023</t>
+          <t>13993</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>79,59%</t>
+          <t>79,81%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>48,15%</t>
+          <t>54,93%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>94,42%</t>
+          <t>94,29%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2502,32 +2502,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>35621</t>
+          <t>40799</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>27645</t>
+          <t>33055</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>41061</t>
+          <t>47012</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>72,28%</t>
+          <t>72,02%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>56,09%</t>
+          <t>58,35%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>83,31%</t>
+          <t>82,98%</t>
         </is>
       </c>
     </row>
@@ -2545,32 +2545,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>20897</t>
+          <t>22780</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>14855</t>
+          <t>15778</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>26880</t>
+          <t>29305</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>54,04%</t>
+          <t>54,48%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>38,42%</t>
+          <t>37,73%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>69,51%</t>
+          <t>70,09%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2580,32 +2580,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>2824</t>
+          <t>3873</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1040</t>
+          <t>1543</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>5726</t>
+          <t>7798</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>26,6%</t>
+          <t>26,1%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>9,8%</t>
+          <t>10,4%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>53,94%</t>
+          <t>52,54%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2615,32 +2615,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>23721</t>
+          <t>26654</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>17687</t>
+          <t>19073</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>30244</t>
+          <t>34104</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>48,13%</t>
+          <t>47,05%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>35,89%</t>
+          <t>33,67%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>61,37%</t>
+          <t>60,2%</t>
         </is>
       </c>
     </row>
@@ -2658,32 +2658,32 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>7278</t>
+          <t>7456</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>2564</t>
+          <t>2696</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>14112</t>
+          <t>15186</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>18,82%</t>
+          <t>17,83%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>6,63%</t>
+          <t>6,45%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>36,49%</t>
+          <t>36,32%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2693,32 +2693,32 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>1336</t>
+          <t>3598</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>163</t>
+          <t>685</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>3748</t>
+          <t>8760</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>12,59%</t>
+          <t>24,24%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>4,62%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>35,31%</t>
+          <t>59,03%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2728,32 +2728,32 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>8614</t>
+          <t>11054</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>3976</t>
+          <t>5490</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>17092</t>
+          <t>19294</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>17,48%</t>
+          <t>19,51%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>8,07%</t>
+          <t>9,69%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>34,68%</t>
+          <t>34,06%</t>
         </is>
       </c>
     </row>
@@ -2771,7 +2771,7 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>2648</t>
+          <t>2582</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
@@ -2781,12 +2781,12 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>8400</t>
+          <t>8103</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>6,85%</t>
+          <t>6,17%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>21,72%</t>
+          <t>19,38%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2841,7 +2841,7 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>2648</t>
+          <t>2582</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
@@ -2851,12 +2851,12 @@
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>8604</t>
+          <t>8257</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>5,37%</t>
+          <t>4,56%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>17,46%</t>
+          <t>14,58%</t>
         </is>
       </c>
     </row>
@@ -2919,7 +2919,7 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>987</t>
+          <t>944</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
@@ -2929,12 +2929,12 @@
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>4240</t>
+          <t>3943</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>9,3%</t>
+          <t>6,36%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
@@ -2944,7 +2944,7 @@
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>39,94%</t>
+          <t>26,57%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2954,7 +2954,7 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>987</t>
+          <t>944</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
@@ -2964,12 +2964,12 @@
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>5677</t>
+          <t>4682</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>1,67%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
@@ -2979,7 +2979,7 @@
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>11,52%</t>
+          <t>8,26%</t>
         </is>
       </c>
     </row>
@@ -3001,32 +3001,32 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>18424</t>
+          <t>23457</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>11796</t>
+          <t>15008</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>25142</t>
+          <t>31407</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>55,7%</t>
+          <t>55,75%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>35,66%</t>
+          <t>35,67%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>76,01%</t>
+          <t>74,65%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3036,32 +3036,32 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>5010</t>
+          <t>5118</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>2345</t>
+          <t>2670</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>6950</t>
+          <t>7213</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>61,93%</t>
+          <t>60,58%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>28,99%</t>
+          <t>31,6%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>85,92%</t>
+          <t>85,38%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3071,27 +3071,27 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>23434</t>
+          <t>28574</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>16657</t>
+          <t>20959</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>30104</t>
+          <t>36946</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>56,93%</t>
+          <t>56,56%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>40,47%</t>
+          <t>41,49%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
@@ -3114,32 +3114,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>22658</t>
+          <t>29864</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>14980</t>
+          <t>20079</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>28683</t>
+          <t>36348</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>68,5%</t>
+          <t>70,99%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>45,29%</t>
+          <t>47,73%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>86,72%</t>
+          <t>86,4%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3149,32 +3149,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>3952</t>
+          <t>4142</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>1509</t>
+          <t>1436</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>6249</t>
+          <t>6582</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>48,85%</t>
+          <t>49,03%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>18,65%</t>
+          <t>17,0%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>77,26%</t>
+          <t>77,92%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3184,32 +3184,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>26610</t>
+          <t>34007</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>17665</t>
+          <t>23913</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>32683</t>
+          <t>40909</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>64,64%</t>
+          <t>67,32%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>42,91%</t>
+          <t>47,34%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>79,39%</t>
+          <t>80,98%</t>
         </is>
       </c>
     </row>
@@ -3227,32 +3227,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>11673</t>
+          <t>15556</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>5892</t>
+          <t>7787</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>19577</t>
+          <t>25229</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>35,29%</t>
+          <t>36,98%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>17,81%</t>
+          <t>18,51%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>59,19%</t>
+          <t>59,97%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3262,32 +3262,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>3506</t>
+          <t>3515</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>1120</t>
+          <t>1190</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>6030</t>
+          <t>6160</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>43,35%</t>
+          <t>41,61%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>13,85%</t>
+          <t>14,09%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>74,54%</t>
+          <t>72,92%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3297,32 +3297,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>15179</t>
+          <t>19071</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>9183</t>
+          <t>11694</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>23557</t>
+          <t>29545</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>36,87%</t>
+          <t>37,75%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>22,31%</t>
+          <t>23,15%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>57,22%</t>
+          <t>58,48%</t>
         </is>
       </c>
     </row>
@@ -3340,32 +3340,32 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>15153</t>
+          <t>16343</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>8666</t>
+          <t>8816</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>21621</t>
+          <t>24412</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>45,81%</t>
+          <t>38,85%</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>26,2%</t>
+          <t>20,96%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>65,37%</t>
+          <t>58,03%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3375,32 +3375,32 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>2845</t>
+          <t>2969</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>959</t>
+          <t>699</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>5450</t>
+          <t>5758</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>35,18%</t>
+          <t>35,15%</t>
         </is>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>11,85%</t>
+          <t>8,27%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>67,38%</t>
+          <t>68,16%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3410,32 +3410,32 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>17999</t>
+          <t>19312</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>11674</t>
+          <t>11423</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>25062</t>
+          <t>28072</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
         <is>
-          <t>43,72%</t>
+          <t>38,23%</t>
         </is>
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>28,36%</t>
+          <t>22,61%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>60,88%</t>
+          <t>55,57%</t>
         </is>
       </c>
     </row>
@@ -3555,7 +3555,7 @@
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
@@ -3570,7 +3570,7 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>4126</t>
+          <t>3823</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
@@ -3580,12 +3580,12 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>6637</t>
+          <t>6084</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>62,17%</t>
+          <t>62,84%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
@@ -3605,27 +3605,27 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>9964</t>
+          <t>10806</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>5565</t>
+          <t>5815</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>12072</t>
+          <t>13550</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>82,53%</t>
+          <t>79,75%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>46,1%</t>
+          <t>42,91%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3640,32 +3640,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>14090</t>
+          <t>14629</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>8251</t>
+          <t>8249</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>17585</t>
+          <t>18153</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>75,31%</t>
+          <t>74,51%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>44,1%</t>
+          <t>42,01%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>93,99%</t>
+          <t>92,46%</t>
         </is>
       </c>
     </row>
@@ -3683,7 +3683,7 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>521</t>
+          <t>507</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
@@ -3693,12 +3693,12 @@
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>6637</t>
+          <t>6084</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>7,85%</t>
+          <t>8,34%</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
@@ -3718,7 +3718,7 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>2349</t>
+          <t>3094</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
@@ -3728,12 +3728,12 @@
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>6945</t>
+          <t>8538</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>19,46%</t>
+          <t>22,84%</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
@@ -3743,7 +3743,7 @@
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>57,53%</t>
+          <t>63,01%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3753,32 +3753,32 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>2870</t>
+          <t>3602</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>517</t>
+          <t>519</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>8295</t>
+          <t>8869</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t>15,34%</t>
+          <t>18,34%</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>2,64%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>44,34%</t>
+          <t>45,17%</t>
         </is>
       </c>
     </row>
@@ -3796,7 +3796,7 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>1941</t>
+          <t>1491</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
@@ -3806,12 +3806,12 @@
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>6092</t>
+          <t>5464</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>29,24%</t>
+          <t>24,51%</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
@@ -3821,7 +3821,7 @@
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>91,79%</t>
+          <t>89,81%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3831,7 +3831,7 @@
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>994</t>
+          <t>993</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
@@ -3841,12 +3841,12 @@
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>5004</t>
+          <t>5902</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>8,23%</t>
+          <t>7,33%</t>
         </is>
       </c>
       <c r="O31" s="2" t="inlineStr">
@@ -3856,7 +3856,7 @@
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>41,45%</t>
+          <t>43,56%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3866,7 +3866,7 @@
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t>2934</t>
+          <t>2485</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
@@ -3876,12 +3876,12 @@
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>8886</t>
+          <t>7972</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
         <is>
-          <t>15,68%</t>
+          <t>12,65%</t>
         </is>
       </c>
       <c r="V31" s="2" t="inlineStr">
@@ -3891,7 +3891,7 @@
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>47,49%</t>
+          <t>40,6%</t>
         </is>
       </c>
     </row>
@@ -3909,7 +3909,7 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>3931</t>
+          <t>3245</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
@@ -3919,12 +3919,12 @@
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>6637</t>
+          <t>6084</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>59,22%</t>
+          <t>53,33%</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
@@ -3944,7 +3944,7 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>921</t>
+          <t>987</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
@@ -3954,12 +3954,12 @@
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>5823</t>
+          <t>5528</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>7,63%</t>
+          <t>7,28%</t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
@@ -3969,7 +3969,7 @@
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>48,23%</t>
+          <t>40,79%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3979,32 +3979,32 @@
       </c>
       <c r="R32" s="2" t="inlineStr">
         <is>
-          <t>4851</t>
+          <t>4231</t>
         </is>
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>927</t>
+          <t>945</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>10483</t>
+          <t>10053</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
         <is>
-          <t>25,93%</t>
+          <t>21,55%</t>
         </is>
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>4,96%</t>
+          <t>4,81%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>56,03%</t>
+          <t>51,2%</t>
         </is>
       </c>
     </row>
@@ -4139,32 +4139,32 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>93492</t>
+          <t>103595</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>80012</t>
+          <t>90089</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>104592</t>
+          <t>116823</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>66,54%</t>
+          <t>65,69%</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>56,94%</t>
+          <t>57,13%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>74,44%</t>
+          <t>74,08%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4174,32 +4174,32 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>39372</t>
+          <t>44832</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>33872</t>
+          <t>36329</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>43767</t>
+          <t>50252</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>77,46%</t>
+          <t>74,42%</t>
         </is>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>66,64%</t>
+          <t>60,31%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>86,11%</t>
+          <t>83,42%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4209,32 +4209,32 @@
       </c>
       <c r="R34" s="2" t="inlineStr">
         <is>
-          <t>132864</t>
+          <t>148427</t>
         </is>
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>119980</t>
+          <t>132289</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>146072</t>
+          <t>162388</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
         <is>
-          <t>69,44%</t>
+          <t>68,1%</t>
         </is>
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>62,71%</t>
+          <t>60,7%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>76,34%</t>
+          <t>74,51%</t>
         </is>
       </c>
     </row>
@@ -4252,32 +4252,32 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>74005</t>
+          <t>85792</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>61086</t>
+          <t>70445</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>86451</t>
+          <t>100006</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>52,67%</t>
+          <t>54,4%</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>43,47%</t>
+          <t>44,67%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>61,53%</t>
+          <t>63,42%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4287,32 +4287,32 @@
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>18592</t>
+          <t>22705</t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>12837</t>
+          <t>15353</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>26644</t>
+          <t>31182</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t>36,58%</t>
+          <t>37,69%</t>
         </is>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>25,26%</t>
+          <t>25,49%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>52,42%</t>
+          <t>51,76%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4322,32 +4322,32 @@
       </c>
       <c r="R35" s="2" t="inlineStr">
         <is>
-          <t>92597</t>
+          <t>108497</t>
         </is>
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>78732</t>
+          <t>91799</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>107637</t>
+          <t>123750</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
         <is>
-          <t>48,39%</t>
+          <t>49,78%</t>
         </is>
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>41,15%</t>
+          <t>42,12%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>56,26%</t>
+          <t>56,78%</t>
         </is>
       </c>
     </row>
@@ -4365,32 +4365,32 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>33436</t>
+          <t>38147</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>23269</t>
+          <t>26600</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>46678</t>
+          <t>53642</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>23,8%</t>
+          <t>24,19%</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>16,56%</t>
+          <t>16,87%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>33,22%</t>
+          <t>34,02%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4400,32 +4400,32 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>11732</t>
+          <t>14782</t>
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>6321</t>
+          <t>8137</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>19064</t>
+          <t>23850</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>23,08%</t>
+          <t>24,54%</t>
         </is>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>12,44%</t>
+          <t>13,51%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>37,51%</t>
+          <t>39,59%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4435,32 +4435,32 @@
       </c>
       <c r="R36" s="2" t="inlineStr">
         <is>
-          <t>45169</t>
+          <t>52929</t>
         </is>
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>32573</t>
+          <t>38486</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>59928</t>
+          <t>70654</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
         <is>
-          <t>23,61%</t>
+          <t>24,29%</t>
         </is>
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>17,02%</t>
+          <t>17,66%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>31,32%</t>
+          <t>32,42%</t>
         </is>
       </c>
     </row>
@@ -4478,32 +4478,32 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>26032</t>
+          <t>26880</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>16138</t>
+          <t>16922</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>37647</t>
+          <t>39856</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>18,53%</t>
+          <t>17,05%</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>11,49%</t>
+          <t>10,73%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>26,79%</t>
+          <t>25,27%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4513,32 +4513,32 @@
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>7280</t>
+          <t>7626</t>
         </is>
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>3392</t>
+          <t>3562</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>13819</t>
+          <t>14887</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>14,32%</t>
+          <t>12,66%</t>
         </is>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>6,67%</t>
+          <t>5,91%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>27,19%</t>
+          <t>24,71%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4548,32 +4548,32 @@
       </c>
       <c r="R37" s="2" t="inlineStr">
         <is>
-          <t>33312</t>
+          <t>34506</t>
         </is>
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>22828</t>
+          <t>23942</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>46419</t>
+          <t>49375</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
         <is>
-          <t>17,41%</t>
+          <t>15,83%</t>
         </is>
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>11,93%</t>
+          <t>10,99%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>24,26%</t>
+          <t>22,66%</t>
         </is>
       </c>
     </row>
@@ -4591,32 +4591,32 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>2971</t>
+          <t>3093</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>848</t>
+          <t>906</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>7287</t>
+          <t>8138</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>1,96%</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>5,19%</t>
+          <t>5,16%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -4626,32 +4626,32 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>4995</t>
+          <t>5064</t>
         </is>
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>1236</t>
+          <t>1157</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>11411</t>
+          <t>11917</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
         <is>
-          <t>9,83%</t>
+          <t>8,41%</t>
         </is>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>1,92%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>22,45%</t>
+          <t>19,78%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -4661,32 +4661,32 @@
       </c>
       <c r="R38" s="2" t="inlineStr">
         <is>
-          <t>7966</t>
+          <t>8157</t>
         </is>
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>3440</t>
+          <t>3617</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>15686</t>
+          <t>15667</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
         <is>
-          <t>4,16%</t>
+          <t>3,74%</t>
         </is>
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>1,66%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>8,2%</t>
+          <t>7,19%</t>
         </is>
       </c>
     </row>
